--- a/2025/data/status.xlsx
+++ b/2025/data/status.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://iattc-my.sharepoint.com/personal/hkxu_iattc_org/Documents/Git/Indicators/2025/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{42AD5D9A-0294-49DC-A0D5-32E50C453CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD7199CD-04C0-404E-BE73-2C0316BCA5AA}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{42AD5D9A-0294-49DC-A0D5-32E50C453CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8EF3921-0512-41BE-A454-C0314ABF03BD}"/>
   <bookViews>
-    <workbookView xWindow="37320" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -160,10 +160,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -430,12 +426,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -443,77 +439,77 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1"/>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B3" s="1"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="1"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B6" s="2"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="1"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="B7" s="2"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="1"/>
+      <c r="B13" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
